--- a/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>EEIQ</t>
   </si>
@@ -656,53 +656,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,29 +722,32 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -762,29 +766,32 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
         <v>800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,29 +810,32 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,8 +854,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +874,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,8 +916,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,8 +960,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -984,8 +1004,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1048,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,29 +1065,30 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3500</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,29 +1107,32 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1151,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,28 +1171,29 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1179,29 +1213,32 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1257,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1261,29 +1301,32 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,29 +1345,32 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1343,8 +1389,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,29 +1433,32 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,29 +1477,32 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1521,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1548,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,28 +1697,31 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1671,29 +1741,32 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1785,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,29 +1829,32 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,34 +1873,37 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,8 +1922,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,29 +1960,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1915,8 +2002,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1956,29 +2046,32 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1997,16 +2090,19 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -2023,8 +2119,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2038,29 +2134,32 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2079,29 +2178,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E46" s="3">
         <v>8800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,29 +2222,32 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>5100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>200</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,29 +2266,32 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,23 +2310,26 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E49" s="3">
         <v>6700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4500</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,8 +2345,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2243,8 +2354,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,29 +2442,32 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2486,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,29 +2530,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E54" s="3">
         <v>19600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2574,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,8 +2612,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2494,17 +2625,17 @@
         <v>2100</v>
       </c>
       <c r="F57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2523,8 +2654,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2564,29 +2698,32 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,29 +2742,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,8 +2786,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2687,26 +2830,29 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2722,14 +2868,17 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,29 +3006,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E66" s="3">
         <v>8000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,8 +3050,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,29 +3244,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4400</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3288,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,29 +3420,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E76" s="3">
         <v>11600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11300</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3278,8 +3464,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,34 +3508,37 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,29 +3557,32 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
-        <v>-3700</v>
-      </c>
       <c r="F81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,8 +3601,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,8 +3621,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3432,7 +3631,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -3441,10 +3640,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3464,8 +3663,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,29 +3883,32 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,8 +3927,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,8 +3947,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3742,11 +3963,11 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3756,8 +3977,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -3768,8 +3989,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,29 +4077,32 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3891,8 +4121,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,8 +4141,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3949,8 +4183,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,29 +4315,32 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,16 +4359,19 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -4139,8 +4388,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4154,29 +4403,32 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4193,6 +4445,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
   <si>
     <t>EEIQ</t>
   </si>
@@ -656,60 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -725,35 +725,41 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="E8" s="3">
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="F8" s="3">
-        <v>2300</v>
+        <v>1100</v>
       </c>
       <c r="G8" s="3">
-        <v>4100</v>
+        <v>1100</v>
       </c>
       <c r="H8" s="3">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="I8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -769,35 +775,41 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E9" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F9" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3">
+        <v>400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>400</v>
+      </c>
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="H9" s="3">
-        <v>700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -813,35 +825,41 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="E10" s="3">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="F10" s="3">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="G10" s="3">
-        <v>2800</v>
+        <v>800</v>
       </c>
       <c r="H10" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="I10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +875,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +899,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +945,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,31 +995,37 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1007,31 +1045,37 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,8 +1095,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,35 +1116,37 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6200</v>
+        <v>4200</v>
       </c>
       <c r="E17" s="3">
-        <v>6600</v>
+        <v>4200</v>
       </c>
       <c r="F17" s="3">
-        <v>6100</v>
+        <v>3100</v>
       </c>
       <c r="G17" s="3">
-        <v>7400</v>
+        <v>3100</v>
       </c>
       <c r="H17" s="3">
         <v>3300</v>
       </c>
       <c r="I17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K17" s="3">
         <v>3500</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,35 +1162,41 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3900</v>
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
-        <v>-3200</v>
+        <v>-2100</v>
       </c>
       <c r="F18" s="3">
-        <v>-3800</v>
+        <v>-2000</v>
       </c>
       <c r="G18" s="3">
-        <v>-3300</v>
+        <v>-2000</v>
       </c>
       <c r="H18" s="3">
-        <v>-1100</v>
+        <v>-1600</v>
       </c>
       <c r="I18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1212,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,34 +1236,36 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>800</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1216,35 +1282,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3500</v>
+        <v>-1700</v>
       </c>
       <c r="E21" s="3">
-        <v>-3000</v>
+        <v>-1700</v>
       </c>
       <c r="F21" s="3">
-        <v>-3700</v>
+        <v>-1800</v>
       </c>
       <c r="G21" s="3">
-        <v>-2400</v>
+        <v>-1800</v>
       </c>
       <c r="H21" s="3">
-        <v>-1000</v>
+        <v>-1500</v>
       </c>
       <c r="I21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,31 +1332,37 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1304,35 +1382,41 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3700</v>
+        <v>-1800</v>
       </c>
       <c r="E23" s="3">
-        <v>-3200</v>
+        <v>-1800</v>
       </c>
       <c r="F23" s="3">
-        <v>-3800</v>
+        <v>-1900</v>
       </c>
       <c r="G23" s="3">
-        <v>-2500</v>
+        <v>-1900</v>
       </c>
       <c r="H23" s="3">
-        <v>-1000</v>
+        <v>-1600</v>
       </c>
       <c r="I23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,34 +1432,40 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-100</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1392,8 +1482,14 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,35 +1532,41 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4200</v>
+        <v>-1800</v>
       </c>
       <c r="E26" s="3">
-        <v>-3000</v>
+        <v>-1800</v>
       </c>
       <c r="F26" s="3">
-        <v>-3600</v>
+        <v>-2100</v>
       </c>
       <c r="G26" s="3">
-        <v>-2500</v>
+        <v>-2100</v>
       </c>
       <c r="H26" s="3">
-        <v>-800</v>
+        <v>-1500</v>
       </c>
       <c r="I26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,35 +1582,41 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4200</v>
+        <v>-1600</v>
       </c>
       <c r="E27" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="F27" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="G27" s="3">
-        <v>-2500</v>
+        <v>-2000</v>
       </c>
       <c r="H27" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="I27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,8 +1632,14 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1682,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1732,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1782,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,34 +1832,40 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-800</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1744,35 +1882,41 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4200</v>
+        <v>-1600</v>
       </c>
       <c r="E33" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="F33" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="G33" s="3">
-        <v>-2500</v>
+        <v>-2000</v>
       </c>
       <c r="H33" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="I33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1788,8 +1932,14 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,35 +1982,41 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4200</v>
+        <v>-1600</v>
       </c>
       <c r="E35" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="F35" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="G35" s="3">
-        <v>-2500</v>
+        <v>-2000</v>
       </c>
       <c r="H35" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="I35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,40 +2032,46 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1925,8 +2087,14 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2111,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,35 +2131,37 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>600</v>
+      </c>
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H41" s="3">
         <v>5900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="G41" s="3">
-        <v>12900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>16500</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2177,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2049,34 +2227,40 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="3">
         <v>1100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1500</v>
       </c>
       <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K43" s="3">
+        <v>1100</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
@@ -2093,8 +2277,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2104,17 +2294,17 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2122,11 +2312,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2137,35 +2327,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,35 +2377,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F46" s="3">
         <v>8700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H46" s="3">
         <v>8800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J46" s="3">
         <v>14100</v>
       </c>
-      <c r="G46" s="3">
-        <v>15500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>19600</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,35 +2427,41 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>5100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2269,35 +2477,41 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="E48" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="F48" s="3">
         <v>3200</v>
       </c>
       <c r="G48" s="3">
-        <v>3700</v>
+        <v>3200</v>
       </c>
       <c r="H48" s="3">
-        <v>4100</v>
+        <v>3500</v>
       </c>
       <c r="I48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,32 +2527,38 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F49" s="3">
         <v>7300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H49" s="3">
         <v>6700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J49" s="3">
         <v>1300</v>
       </c>
-      <c r="G49" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,17 +2568,23 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2627,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,35 +2677,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,8 +2727,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,35 +2777,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F54" s="3">
         <v>19200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="H54" s="3">
         <v>19600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J54" s="3">
         <v>24000</v>
       </c>
-      <c r="G54" s="3">
-        <v>26200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>24000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2827,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2851,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,35 +2871,37 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2657,31 +2917,37 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2701,35 +2967,41 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4800</v>
+        <v>2600</v>
       </c>
       <c r="E59" s="3">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="F59" s="3">
-        <v>3900</v>
+        <v>5800</v>
       </c>
       <c r="G59" s="3">
-        <v>3700</v>
+        <v>5800</v>
       </c>
       <c r="H59" s="3">
-        <v>5700</v>
+        <v>1500</v>
       </c>
       <c r="I59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,35 +3017,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F60" s="3">
         <v>6900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J60" s="3">
         <v>6100</v>
       </c>
-      <c r="G60" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,31 +3067,37 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2833,32 +3117,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="F62" s="3">
-        <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>500</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2871,14 +3161,20 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3217,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3267,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,35 +3317,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10100</v>
+        <v>7400</v>
       </c>
       <c r="E66" s="3">
-        <v>8000</v>
+        <v>7400</v>
       </c>
       <c r="F66" s="3">
-        <v>8900</v>
+        <v>8300</v>
       </c>
       <c r="G66" s="3">
-        <v>9900</v>
+        <v>8300</v>
       </c>
       <c r="H66" s="3">
-        <v>9100</v>
+        <v>5600</v>
       </c>
       <c r="I66" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K66" s="3">
         <v>4000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3367,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3391,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3437,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3487,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3537,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,35 +3587,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="H72" s="3">
         <v>-5600</v>
       </c>
-      <c r="F72" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>3700</v>
-      </c>
       <c r="I72" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K72" s="3">
         <v>4400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3291,8 +3637,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3687,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3737,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,35 +3787,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F76" s="3">
         <v>9100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H76" s="3">
         <v>11600</v>
       </c>
-      <c r="F76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>16300</v>
-      </c>
-      <c r="H76" s="3">
-        <v>14900</v>
-      </c>
       <c r="I76" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K76" s="3">
         <v>11300</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3837,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,40 +3887,46 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3560,35 +3942,41 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4200</v>
+        <v>-1600</v>
       </c>
       <c r="E81" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="F81" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="G81" s="3">
-        <v>-2500</v>
+        <v>-2000</v>
       </c>
       <c r="H81" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="I81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,8 +3992,14 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,16 +4016,18 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -3643,13 +4039,13 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3666,8 +4062,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +4112,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +4162,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4212,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4262,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,35 +4312,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-900</v>
+        <v>-5000</v>
       </c>
       <c r="E89" s="3">
-        <v>-4300</v>
+        <v>-5000</v>
       </c>
       <c r="F89" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="G89" s="3">
-        <v>-3200</v>
+        <v>-500</v>
       </c>
       <c r="H89" s="3">
-        <v>3200</v>
+        <v>-2200</v>
       </c>
       <c r="I89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,8 +4362,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,8 +4386,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3966,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -3980,11 +4420,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -3992,8 +4432,14 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4482,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,35 +4532,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1400</v>
+        <v>2200</v>
       </c>
       <c r="E94" s="3">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="F94" s="3">
-        <v>-500</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4582,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,31 +4606,33 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4186,8 +4652,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4702,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4752,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,35 +4802,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1500</v>
+        <v>600</v>
       </c>
       <c r="F100" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>4400</v>
+        <v>-700</v>
       </c>
       <c r="I100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>200</v>
+      </c>
+      <c r="K100" s="3">
         <v>4900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4852,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4373,11 +4869,11 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -4391,11 +4887,11 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4406,35 +4902,41 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-900</v>
+        <v>-2200</v>
       </c>
       <c r="E102" s="3">
-        <v>-5200</v>
+        <v>-2200</v>
       </c>
       <c r="F102" s="3">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="G102" s="3">
-        <v>-3600</v>
+        <v>-400</v>
       </c>
       <c r="H102" s="3">
-        <v>7200</v>
+        <v>-2600</v>
       </c>
       <c r="I102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4448,6 +4950,12 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
   <si>
     <t>EEIQ</t>
   </si>
@@ -656,66 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,41 +733,47 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="3">
         <v>2100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -781,22 +789,28 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
         <v>900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -808,14 +822,14 @@
         <v>400</v>
       </c>
       <c r="K9" s="3">
+        <v>400</v>
+      </c>
+      <c r="L9" s="3">
+        <v>400</v>
+      </c>
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,41 +845,47 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,8 +901,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -901,8 +927,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -951,8 +979,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,8 +1035,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,11 +1067,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1051,8 +1091,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,10 +1124,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1101,8 +1147,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1118,41 +1170,43 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F17" s="3">
         <v>4200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,41 +1222,47 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1218,8 +1278,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1238,40 +1304,42 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1288,41 +1356,47 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,8 +1412,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1364,11 +1444,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1388,41 +1468,47 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,8 +1524,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1450,16 +1542,16 @@
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-100</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
@@ -1467,11 +1559,11 @@
       <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-100</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1488,8 +1580,14 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1538,41 +1636,47 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,41 +1692,47 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1748,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1688,8 +1804,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1738,8 +1860,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1788,8 +1916,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1838,40 +1972,46 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1888,41 +2028,47 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1938,8 +2084,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1988,41 +2140,47 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,46 +2196,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2257,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2113,8 +2283,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2133,41 +2305,43 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,8 +2357,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2233,40 +2413,46 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1700</v>
       </c>
       <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1100</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2283,8 +2469,14 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2306,11 +2498,11 @@
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -2318,11 +2510,11 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2333,8 +2525,14 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2359,15 +2557,15 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,41 +2581,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F46" s="3">
         <v>10800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2637,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2456,18 +2666,18 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>5100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2483,41 +2693,47 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2533,38 +2749,44 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F49" s="3">
         <v>7200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,17 +2796,23 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2633,8 +2861,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2683,16 +2917,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7500</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2709,15 +2949,15 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2973,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2783,41 +3029,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F54" s="3">
         <v>20500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>24000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>15400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,8 +3085,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2853,8 +3111,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2873,41 +3133,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,38 +3185,44 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2973,41 +3241,47 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,41 +3297,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F60" s="3">
         <v>6300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,38 +3353,44 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3123,8 +3409,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3140,21 +3432,21 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,14 +3459,20 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3223,8 +3521,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3273,8 +3577,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3323,41 +3633,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F66" s="3">
         <v>7400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3373,8 +3689,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3393,8 +3715,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3443,8 +3767,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3493,8 +3823,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3543,8 +3879,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3593,41 +3935,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-12300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-12300</v>
       </c>
-      <c r="F72" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-9100</v>
-      </c>
       <c r="H72" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-5600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-5600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-2300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3991,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3693,8 +4047,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3743,8 +4103,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3793,41 +4159,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11300</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +4215,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3893,46 +4271,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3948,41 +4332,47 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4388,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4018,16 +4414,18 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4042,16 +4440,16 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -4068,8 +4466,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4118,8 +4522,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4168,8 +4578,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4218,8 +4634,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4268,8 +4690,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4318,41 +4746,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4802,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4388,8 +4828,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4426,11 +4868,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4438,8 +4880,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4488,8 +4936,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4538,41 +4992,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F94" s="3">
         <v>2200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>2200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4588,8 +5048,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4608,8 +5074,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4634,11 +5102,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4658,8 +5126,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4708,8 +5182,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4758,8 +5238,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4808,41 +5294,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4858,8 +5350,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4875,11 +5373,11 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4893,11 +5391,11 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4908,41 +5406,47 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4956,6 +5460,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="92">
   <si>
     <t>EEIQ</t>
   </si>
@@ -750,11 +750,11 @@
       <c r="E8" s="3">
         <v>2000</v>
       </c>
-      <c r="F8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2100</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>1100</v>
@@ -762,8 +762,8 @@
       <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
-        <v>1700</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>1700</v>
@@ -806,11 +806,11 @@
       <c r="E9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
-        <v>900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>900</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -818,8 +818,8 @@
       <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
-        <v>400</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>400</v>
@@ -862,11 +862,11 @@
       <c r="E10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1200</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>800</v>
@@ -874,8 +874,8 @@
       <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3">
-        <v>1300</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>1300</v>
@@ -1109,10 +1109,10 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1121,7 +1121,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1183,11 +1183,11 @@
       <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4200</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>3100</v>
@@ -1195,8 +1195,8 @@
       <c r="I17" s="3">
         <v>3100</v>
       </c>
-      <c r="J17" s="3">
-        <v>3300</v>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>3300</v>
@@ -1239,11 +1239,11 @@
       <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2100</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-1900</v>
@@ -1251,8 +1251,8 @@
       <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
-        <v>-1600</v>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-1600</v>
@@ -1317,11 +1317,11 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-200</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -1329,8 +1329,8 @@
       <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>-1500</v>
       </c>
       <c r="F21" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-1700</v>
@@ -1386,7 +1386,7 @@
         <v>-1700</v>
       </c>
       <c r="J21" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-1500</v>
@@ -1485,11 +1485,11 @@
       <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1800</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-1800</v>
@@ -1497,8 +1497,8 @@
       <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
-        <v>-1600</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>-1600</v>
@@ -1541,11 +1541,11 @@
       <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-100</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
@@ -1553,8 +1553,8 @@
       <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>-100</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
@@ -1653,11 +1653,11 @@
       <c r="E26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1800</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-2000</v>
@@ -1665,8 +1665,8 @@
       <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
-        <v>-1500</v>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>-1500</v>
@@ -1709,11 +1709,11 @@
       <c r="E27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1600</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-2000</v>
@@ -1721,8 +1721,8 @@
       <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
-        <v>-1300</v>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>-1300</v>
@@ -1989,11 +1989,11 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3">
-        <v>200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>200</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
@@ -2001,8 +2001,8 @@
       <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2045,11 +2045,11 @@
       <c r="E33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1600</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-2000</v>
@@ -2057,8 +2057,8 @@
       <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
-        <v>-1300</v>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>-1300</v>
@@ -2157,11 +2157,11 @@
       <c r="E35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1600</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-2000</v>
@@ -2169,8 +2169,8 @@
       <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
-        <v>-1300</v>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>-1300</v>
@@ -2318,11 +2318,11 @@
       <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
-        <v>600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>600</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>5000</v>
@@ -2330,8 +2330,8 @@
       <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="J41" s="3">
-        <v>5900</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>5900</v>
@@ -2430,11 +2430,11 @@
       <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1200</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>1000</v>
@@ -2442,8 +2442,8 @@
       <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
-        <v>1100</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>1100</v>
@@ -2486,11 +2486,11 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -2498,8 +2498,8 @@
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2598,11 +2598,11 @@
       <c r="E46" s="3">
         <v>4300</v>
       </c>
-      <c r="F46" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>10800</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>8700</v>
@@ -2610,8 +2610,8 @@
       <c r="I46" s="3">
         <v>8700</v>
       </c>
-      <c r="J46" s="3">
-        <v>8800</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>8800</v>
@@ -2710,11 +2710,11 @@
       <c r="E48" s="3">
         <v>4400</v>
       </c>
-      <c r="F48" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2500</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>3200</v>
@@ -2722,8 +2722,8 @@
       <c r="I48" s="3">
         <v>3200</v>
       </c>
-      <c r="J48" s="3">
-        <v>3500</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>3500</v>
@@ -2766,11 +2766,11 @@
       <c r="E49" s="3">
         <v>7100</v>
       </c>
-      <c r="F49" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>7200</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>7300</v>
@@ -2778,8 +2778,8 @@
       <c r="I49" s="3">
         <v>7300</v>
       </c>
-      <c r="J49" s="3">
-        <v>6700</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>6700</v>
@@ -3046,11 +3046,11 @@
       <c r="E54" s="3">
         <v>23300</v>
       </c>
-      <c r="F54" s="3">
-        <v>20500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>20500</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>19200</v>
@@ -3058,8 +3058,8 @@
       <c r="I54" s="3">
         <v>19200</v>
       </c>
-      <c r="J54" s="3">
-        <v>19600</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>19600</v>
@@ -3146,11 +3146,11 @@
       <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2700</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
@@ -3158,8 +3158,8 @@
       <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
-        <v>2100</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>2100</v>
@@ -3202,11 +3202,11 @@
       <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="F58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1000</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
@@ -3214,8 +3214,8 @@
       <c r="I58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
-        <v>800</v>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>800</v>
@@ -3258,11 +3258,11 @@
       <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2600</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>5800</v>
@@ -3270,8 +3270,8 @@
       <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
-        <v>1500</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>1500</v>
@@ -3314,11 +3314,11 @@
       <c r="E60" s="3">
         <v>9800</v>
       </c>
-      <c r="F60" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6300</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>6900</v>
@@ -3326,8 +3326,8 @@
       <c r="I60" s="3">
         <v>6900</v>
       </c>
-      <c r="J60" s="3">
-        <v>4400</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>4400</v>
@@ -3371,10 +3371,10 @@
         <v>2200</v>
       </c>
       <c r="F61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>600</v>
@@ -3383,7 +3383,7 @@
         <v>600</v>
       </c>
       <c r="J61" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>800</v>
@@ -3438,8 +3438,8 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3650,11 +3650,11 @@
       <c r="E66" s="3">
         <v>12400</v>
       </c>
-      <c r="F66" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G66" s="3">
-        <v>7400</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>8300</v>
@@ -3662,8 +3662,8 @@
       <c r="I66" s="3">
         <v>8300</v>
       </c>
-      <c r="J66" s="3">
-        <v>5600</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>5600</v>
@@ -3952,11 +3952,11 @@
       <c r="E72" s="3">
         <v>-15000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-12300</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-9000</v>
@@ -3964,8 +3964,8 @@
       <c r="I72" s="3">
         <v>-9000</v>
       </c>
-      <c r="J72" s="3">
-        <v>-5600</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>-5600</v>
@@ -4176,11 +4176,11 @@
       <c r="E76" s="3">
         <v>5200</v>
       </c>
-      <c r="F76" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>7100</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>9100</v>
@@ -4188,8 +4188,8 @@
       <c r="I76" s="3">
         <v>9100</v>
       </c>
-      <c r="J76" s="3">
-        <v>11600</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>11600</v>
@@ -4349,11 +4349,11 @@
       <c r="E81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1600</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-2000</v>
@@ -4361,8 +4361,8 @@
       <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
-        <v>-1300</v>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>-1300</v>
@@ -4427,11 +4427,11 @@
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -4439,8 +4439,8 @@
       <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>100</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -4763,11 +4763,11 @@
       <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-5000</v>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
         <v>-500</v>
@@ -4775,8 +4775,8 @@
       <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
-        <v>-2200</v>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>-2200</v>
@@ -4841,11 +4841,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4853,8 +4853,8 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5009,11 +5009,11 @@
       <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2200</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
@@ -5021,8 +5021,8 @@
       <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>300</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>300</v>
@@ -5311,11 +5311,11 @@
       <c r="E100" s="3">
         <v>1900</v>
       </c>
-      <c r="F100" s="3">
-        <v>600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>600</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>100</v>
@@ -5323,8 +5323,8 @@
       <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>-700</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>-700</v>
@@ -5367,11 +5367,11 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -5424,10 +5424,10 @@
         <v>300</v>
       </c>
       <c r="F102" s="3">
-        <v>-2200</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-2200</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-400</v>
@@ -5436,7 +5436,7 @@
         <v>-400</v>
       </c>
       <c r="J102" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-2600</v>

--- a/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EEIQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="92">
   <si>
     <t>EEIQ</t>
   </si>
@@ -656,81 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -746,53 +748,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,53 +816,59 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
-        <v>600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>600</v>
-      </c>
       <c r="H9" s="3">
+        <v>500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>400</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,53 +884,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1400</v>
-      </c>
       <c r="H10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
         <v>1300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -932,8 +952,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +982,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1018,8 +1046,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1080,16 +1114,22 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-300</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1097,11 +1137,11 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -1118,11 +1158,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1142,8 +1182,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1172,19 +1218,19 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1204,8 +1250,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1225,53 +1277,55 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="3">
         <v>3700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,53 +1341,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,8 +1409,14 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1373,52 +1439,54 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1435,28 +1503,34 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H21" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="I21" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="J21" s="3">
         <v>-1700</v>
@@ -1465,23 +1539,23 @@
         <v>-1700</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="M21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,8 +1571,14 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1535,11 +1615,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1559,28 +1639,34 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1800</v>
       </c>
       <c r="J23" s="3">
         <v>-1800</v>
@@ -1588,24 +1674,24 @@
       <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>-1800</v>
       </c>
       <c r="M23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1707,14 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1633,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>-100</v>
@@ -1645,28 +1737,28 @@
         <v>-100</v>
       </c>
       <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-100</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-100</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1683,8 +1775,14 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1745,53 +1843,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,53 +1911,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1869,8 +1979,14 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1931,8 +2047,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1993,8 +2115,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2055,8 +2183,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2117,52 +2251,58 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2179,53 +2319,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2387,14 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2303,53 +2455,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,58 +2523,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2596,14 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2456,8 +2626,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2480,53 +2652,55 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>11400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,8 +2716,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2604,52 +2784,58 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1400</v>
-      </c>
       <c r="H43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1700</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1100</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2666,8 +2852,14 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2695,8 +2887,8 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2704,8 +2896,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -2713,11 +2905,11 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2728,8 +2920,14 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2766,15 +2964,15 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,53 +2988,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F46" s="3">
         <v>2500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>8800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2852,8 +3056,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2887,18 +3097,18 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>5100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2914,53 +3124,59 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
         <v>3500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,50 +3192,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F49" s="3">
         <v>7000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>7300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3">
         <v>6700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,17 +3251,23 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3100,8 +3328,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3162,16 +3396,22 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>7500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7500</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>7500</v>
@@ -3179,11 +3419,11 @@
       <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7500</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -3200,15 +3440,15 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3464,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3286,53 +3532,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F54" s="3">
         <v>20000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>23300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>23300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>19200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>19600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>24000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>15400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3600,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3372,8 +3630,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3396,53 +3656,55 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3458,50 +3720,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3520,53 +3788,59 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3582,53 +3856,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F60" s="3">
         <v>6400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,50 +3924,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3706,8 +3992,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3738,18 +4030,18 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3762,14 +4054,20 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3830,8 +4128,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3892,8 +4196,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3954,53 +4264,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F66" s="3">
         <v>8900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>5600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4016,8 +4332,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4040,8 +4362,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4102,8 +4426,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4164,8 +4494,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4226,8 +4562,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4288,53 +4630,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-15200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-15200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-15000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-15000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-12300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-12300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-9000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-9000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>-5600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-2300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4350,8 +4698,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4412,8 +4766,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4474,8 +4834,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4536,53 +4902,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3">
         <v>11600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4598,8 +4970,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4660,58 +5038,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4727,53 +5111,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +5179,14 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4813,8 +5209,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4825,10 +5223,10 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -4837,28 +5235,28 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4875,8 +5273,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4937,8 +5341,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4999,8 +5409,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5061,8 +5477,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5123,8 +5545,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5185,53 +5613,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5247,8 +5681,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5271,22 +5711,24 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5300,14 +5742,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5321,11 +5763,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5333,8 +5775,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5395,8 +5843,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5457,53 +5911,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5519,8 +5979,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5543,8 +6009,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5581,11 +6049,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5605,8 +6073,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5667,8 +6141,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5729,8 +6209,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5791,53 +6277,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1900</v>
+      <c r="D100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>4900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5853,8 +6345,14 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5876,8 +6374,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5885,8 +6383,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -5900,11 +6398,11 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -5915,53 +6413,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,6 +6479,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
